--- a/mapping/STG_DTM/Mapping_STG_FCT_CLOS_COLLATERAL.xlsx
+++ b/mapping/STG_DTM/Mapping_STG_FCT_CLOS_COLLATERAL.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,6 +163,10 @@
       <family val="1"/>
       <b val="1"/>
       <strike val="0"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -234,7 +238,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -394,6 +398,9 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -699,15 +706,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -727,7 +734,6 @@
           <t>SB_DWH.FCT_CLOS_COLLATERAL AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -741,7 +747,6 @@
         </is>
       </c>
       <c r="E2" s="52" t="n"/>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -755,7 +760,6 @@
         </is>
       </c>
       <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -769,57 +773,46 @@
         </is>
       </c>
       <c r="E4" s="52" t="n"/>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="n"/>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
       <c r="E6" s="52" t="n"/>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -847,9 +840,8 @@
           <t>How to mapping CLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -863,9 +855,8 @@
           <t>A.DAYID = v_batch_date</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -881,17 +872,16 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK (1/2) — Driving: FCT_CLOS_COLLATERAL (SB_DWH). Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>A.DAYID</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
@@ -909,17 +899,16 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>PK (2/2) — khóa nghiệp vụ của dòng tài sản</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>A.COLLATERAL_BK</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
@@ -937,19 +926,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_CLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>A.APPLICATION_SK</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>COLLATERAL_TYPE_CODE</t>
@@ -965,17 +953,16 @@
           <t>Loại tài sản bảo đảm</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>Loại tài sản bảo đảm — DENORMALIZE TRỰC TIẾP (text tự do tiếng Việt không dấu)</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>A.COLLATERAL_TYPE_CODE</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
@@ -993,17 +980,16 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng CLOS</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -1021,17 +1007,16 @@
           <t>Diễn giải tài sản bảo đảm</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Diễn giải tài sản bảo đảm (CLOB)</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.DESCRIPTION</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -1049,17 +1034,16 @@
           <t>Chủ sở hữu tài sản</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Chủ sở hữu tài sản</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.OWNER_NAME</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1077,17 +1061,16 @@
           <t>Phương thức quản lý tài sản</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Phương thức quản lý tài sản</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.COLL_MGMT_METHOD</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
@@ -1105,17 +1088,16 @@
           <t>Giá trị định giá tài sản</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Giá trị định giá của tài sản — lấy nguyên văn, không ép kiểu số</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.APPRAISED_VALUE</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1133,148 +1115,17 @@
           <t>Tỷ lệ cho vay/TSBĐ</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Tỷ lệ cho vay trên giá trị tài sản</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.LOAN_RATE_LTV</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
-    </row>
-    <row r="27" ht="51" customHeight="1"/>
-    <row r="28" ht="34" customHeight="1"/>
-    <row r="29" ht="51" customHeight="1"/>
-    <row r="30" ht="85" customHeight="1"/>
-    <row r="31" ht="85" customHeight="1"/>
-    <row r="32" ht="85" customHeight="1"/>
-    <row r="33" ht="34" customHeight="1"/>
-    <row r="34" ht="85" customHeight="1"/>
-    <row r="35" ht="51" customHeight="1"/>
-    <row r="36" ht="17" customHeight="1"/>
-    <row r="37" ht="51" customHeight="1"/>
-    <row r="38" ht="51" customHeight="1"/>
-    <row r="39" ht="34" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1"/>
-    <row r="41" ht="34" customHeight="1"/>
-    <row r="42" ht="17" customHeight="1"/>
-    <row r="43" ht="34" customHeight="1"/>
-    <row r="44" ht="17" customHeight="1"/>
-    <row r="45" ht="85" customHeight="1"/>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
